--- a/public/template_xls/template_lulusan_new.xlsx
+++ b/public/template_xls/template_lulusan_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SKLV12\public\template_xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97E0039-4254-429F-B384-81B5AAF9E1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28A2207-F540-49AB-851C-D34FBF1A5186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2378E907-CBBD-4B2C-8AC1-931A47C0D843}"/>
   </bookViews>
@@ -718,9 +718,7 @@
       <c r="N4" s="4">
         <v>80</v>
       </c>
-      <c r="O4" s="4">
-        <v>85</v>
-      </c>
+      <c r="O4" s="4"/>
       <c r="P4" s="4">
         <v>90</v>
       </c>
@@ -764,7 +762,7 @@
       </c>
       <c r="M5" s="4">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="N5" s="4">
         <v>75</v>
@@ -772,9 +770,7 @@
       <c r="O5" s="4">
         <v>80</v>
       </c>
-      <c r="P5" s="4">
-        <v>85</v>
-      </c>
+      <c r="P5" s="4"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
@@ -815,11 +811,9 @@
       </c>
       <c r="M6" s="4">
         <f>ROUND(AVERAGE(N6:P6),2)</f>
-        <v>89.67</v>
-      </c>
-      <c r="N6" s="4">
-        <v>88</v>
-      </c>
+        <v>90.5</v>
+      </c>
+      <c r="N6" s="4"/>
       <c r="O6" s="4">
         <v>89</v>
       </c>

--- a/public/template_xls/template_lulusan_new.xlsx
+++ b/public/template_xls/template_lulusan_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SKLV12\public\template_xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28A2207-F540-49AB-851C-D34FBF1A5186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F310EEA2-274D-4A98-AFC0-B1D9EF546FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2378E907-CBBD-4B2C-8AC1-931A47C0D843}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>NO</t>
   </si>
@@ -59,15 +59,6 @@
     <t>KODE_JURUSAN</t>
   </si>
   <si>
-    <t>TEK-678</t>
-  </si>
-  <si>
-    <t>TEK-938</t>
-  </si>
-  <si>
-    <t>REK-970</t>
-  </si>
-  <si>
     <t>NIS</t>
   </si>
   <si>
@@ -98,18 +89,9 @@
     <t>TGL_KELULUSAN</t>
   </si>
   <si>
-    <t>OQD-217</t>
-  </si>
-  <si>
-    <t>ETJ-645</t>
-  </si>
-  <si>
     <t>RATA-RATA</t>
   </si>
   <si>
-    <t>QMN-623</t>
-  </si>
-  <si>
     <t>KODE MATA PELAJARAN</t>
   </si>
   <si>
@@ -138,6 +120,39 @@
   </si>
   <si>
     <t>malik</t>
+  </si>
+  <si>
+    <t>GHT-133</t>
+  </si>
+  <si>
+    <t>VQS-385</t>
+  </si>
+  <si>
+    <t>VGK-313</t>
+  </si>
+  <si>
+    <t>UWS-198</t>
+  </si>
+  <si>
+    <t>IJH-647</t>
+  </si>
+  <si>
+    <t>MUL-551</t>
+  </si>
+  <si>
+    <t>TEK-648</t>
+  </si>
+  <si>
+    <t>REK-922</t>
+  </si>
+  <si>
+    <t>JK</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>P</t>
   </si>
 </sst>
 </file>
@@ -575,82 +590,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B2E66E-983B-4FF3-8E58-FD7EC5FA94DE}">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.33203125" customWidth="1"/>
     <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.88671875" customWidth="1"/>
-    <col min="15" max="16" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5546875" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" customWidth="1"/>
+    <col min="16" max="16" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="10.33203125" customWidth="1"/>
+    <col min="19" max="19" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="K2" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -659,27 +684,34 @@
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
-      <c r="I3" s="6"/>
+      <c r="I3" s="8"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
-      <c r="N3" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="N3" s="6"/>
       <c r="O3" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2">
         <v>123456</v>
@@ -691,44 +723,53 @@
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="3">
+        <v>37</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="3">
         <v>32031</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="3">
-        <v>46103</v>
+        <v>33</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="L4" s="3">
         <v>46103</v>
       </c>
-      <c r="M4" s="4">
-        <f t="shared" ref="M4:M5" si="0">ROUND(AVERAGE(N4:P4),2)</f>
+      <c r="M4" s="3">
+        <v>46103</v>
+      </c>
+      <c r="N4" s="4">
+        <f t="shared" ref="N4:N5" si="0">ROUND(AVERAGE(O4:S4),2)</f>
+        <v>79.5</v>
+      </c>
+      <c r="O4" s="4">
+        <v>80</v>
+      </c>
+      <c r="P4" s="4">
         <v>85</v>
       </c>
-      <c r="N4" s="4">
-        <v>80</v>
-      </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4">
-        <v>90</v>
-      </c>
+      <c r="Q4" s="4">
+        <v>78</v>
+      </c>
+      <c r="R4" s="4">
+        <v>75</v>
+      </c>
+      <c r="S4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2">
         <v>123457</v>
@@ -740,44 +781,53 @@
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="3">
+        <v>37</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="3">
         <v>32358</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="3">
-        <v>46103</v>
+        <v>34</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="L5" s="3">
         <v>46103</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="3">
+        <v>46103</v>
+      </c>
+      <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>77.5</v>
-      </c>
-      <c r="N5" s="4">
+        <v>78.75</v>
+      </c>
+      <c r="O5" s="4">
         <v>75</v>
       </c>
-      <c r="O5" s="4">
+      <c r="P5" s="4">
         <v>80</v>
       </c>
-      <c r="P5" s="4"/>
+      <c r="Q5" s="4">
+        <v>75</v>
+      </c>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4">
+        <v>85</v>
+      </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2">
         <v>123458</v>
@@ -789,39 +839,48 @@
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="3">
+        <v>38</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="3">
         <v>31537</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="3">
-        <v>46103</v>
+        <v>35</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="L6" s="3">
         <v>46103</v>
       </c>
-      <c r="M6" s="4">
-        <f>ROUND(AVERAGE(N6:P6),2)</f>
-        <v>90.5</v>
-      </c>
-      <c r="N6" s="4"/>
+      <c r="M6" s="3">
+        <v>46103</v>
+      </c>
+      <c r="N6" s="4">
+        <f>ROUND(AVERAGE(O6:S6),2)</f>
+        <v>87.25</v>
+      </c>
       <c r="O6" s="4">
+        <v>88</v>
+      </c>
+      <c r="P6" s="4">
         <v>89</v>
       </c>
-      <c r="P6" s="4">
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4">
+        <v>80</v>
+      </c>
+      <c r="S6" s="4">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -838,23 +897,27 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:P2"/>
+  <mergeCells count="15">
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:S2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
-    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="M2:M3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
